--- a/etf_holdings/2026-09-17_common_holdings_all.xlsx
+++ b/etf_holdings/2026-09-17_common_holdings_all.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="AD2" t="n">
@@ -800,7 +800,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>109.51%</t>
+          <t>109.55%</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>8.34%</t>
+          <t>8.32%</t>
         </is>
       </c>
       <c r="AD3" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>70.07%</t>
+          <t>70.05%</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>4.13%</t>
+          <t>3.83%</t>
         </is>
       </c>
       <c r="AD4" t="n">
@@ -1172,12 +1172,12 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>58.52%</t>
+          <t>58.22%</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>4.88%</t>
+          <t>4.85%</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>4.60%</t>
+          <t>4.64%</t>
         </is>
       </c>
       <c r="AD5" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>52.04%</t>
+          <t>52.08%</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
